--- a/AÑO 2026/Registro bauchers.xlsx
+++ b/AÑO 2026/Registro bauchers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\AÑO 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6893A96B-4074-411D-A084-9A69273692D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B39A9E-EDF1-4DEA-B579-6452B167F436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="120">
   <si>
     <t xml:space="preserve">Concepto </t>
   </si>
@@ -1414,9 +1414,7 @@
         <f t="shared" ref="I2:I38" si="0">TEXT(D2,"mmmm")</f>
         <v>enero</v>
       </c>
-      <c r="K2" s="33" t="s">
-        <v>62</v>
-      </c>
+      <c r="K2" s="33"/>
       <c r="M2" t="s">
         <v>41</v>
       </c>

--- a/AÑO 2026/Registro bauchers.xlsx
+++ b/AÑO 2026/Registro bauchers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\AÑO 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B39A9E-EDF1-4DEA-B579-6452B167F436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7E5B4A-2F1C-470E-8056-7D50D48CB54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
   <sheets>
     <sheet name="BAUCHER 2026" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="119">
   <si>
     <t xml:space="preserve">Concepto </t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>IUAN MARIA OSORNO VILLATORO</t>
-  </si>
-  <si>
-    <t>03/032026</t>
   </si>
   <si>
     <t>T-4CHCQJ</t>
@@ -1376,13 +1373,13 @@
         <v>12</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K1" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -1408,7 +1405,7 @@
         <v>1510</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I2" s="11" t="str">
         <f t="shared" ref="I2:I38" si="0">TEXT(D2,"mmmm")</f>
@@ -1416,15 +1413,15 @@
       </c>
       <c r="K2" s="33"/>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -1489,10 +1486,10 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -1523,10 +1520,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -1544,7 +1541,7 @@
         <v>1510</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I6" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1557,10 +1554,10 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -1588,10 +1585,10 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>7</v>
@@ -1609,7 +1606,7 @@
         <v>1510</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I8" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1618,10 +1615,10 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -1648,10 +1645,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
@@ -1669,7 +1666,7 @@
         <v>1510</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I10" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1678,10 +1675,10 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -1699,7 +1696,7 @@
         <v>1510</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I11" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1708,10 +1705,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>7</v>
@@ -1729,7 +1726,7 @@
         <v>1510</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I12" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1738,10 +1735,10 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -1759,7 +1756,7 @@
         <v>1510</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I13" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1768,10 +1765,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>61</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>7</v>
@@ -1789,7 +1786,7 @@
         <v>1510</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I14" s="11" t="str">
         <f>TEXT(D14,"mmmm")</f>
@@ -1798,10 +1795,10 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -1819,7 +1816,7 @@
         <v>1510</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I15" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1828,10 +1825,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>7</v>
@@ -1849,7 +1846,7 @@
         <v>1510</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I16" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1858,10 +1855,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>7</v>
@@ -1879,7 +1876,7 @@
         <v>1510</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1888,10 +1885,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>52</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>53</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>7</v>
@@ -1909,7 +1906,7 @@
         <v>1510</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I18" s="11" t="str">
         <f t="shared" si="0"/>
@@ -1918,10 +1915,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>63</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>7</v>
@@ -1939,7 +1936,7 @@
         <v>1510</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I19" s="11" t="str">
         <f t="shared" ref="I19:I35" si="1">TEXT(D19,"mmmm")</f>
@@ -1948,10 +1945,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>7</v>
@@ -1969,7 +1966,7 @@
         <v>1510</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I20" s="11" t="str">
         <f t="shared" si="1"/>
@@ -1978,10 +1975,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>7</v>
@@ -1999,7 +1996,7 @@
         <v>1510</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I21" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2008,10 +2005,10 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>66</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>67</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>7</v>
@@ -2029,7 +2026,7 @@
         <v>1510</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I22" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2038,10 +2035,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -2059,7 +2056,7 @@
         <v>1510</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I23" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2068,10 +2065,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>7</v>
@@ -2089,7 +2086,7 @@
         <v>1510</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I24" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2098,10 +2095,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>7</v>
@@ -2119,7 +2116,7 @@
         <v>1510</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I25" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2128,10 +2125,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>7</v>
@@ -2149,7 +2146,7 @@
         <v>1510</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I26" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2158,10 +2155,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>7</v>
@@ -2179,7 +2176,7 @@
         <v>1510</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I27" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2188,10 +2185,10 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>74</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>75</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>7</v>
@@ -2209,7 +2206,7 @@
         <v>1510</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I28" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2218,10 +2215,10 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>7</v>
@@ -2239,7 +2236,7 @@
         <v>1510</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I29" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2299,7 +2296,7 @@
         <v>1510</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I31" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2329,7 +2326,7 @@
         <v>2510</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I32" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2359,7 +2356,7 @@
         <v>1510</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I33" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2389,7 +2386,7 @@
         <v>2510</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I34" s="11" t="str">
         <f t="shared" si="1"/>
@@ -2409,8 +2406,8 @@
       <c r="D35" s="11">
         <v>46063</v>
       </c>
-      <c r="E35" s="11" t="s">
-        <v>25</v>
+      <c r="E35" s="11">
+        <v>46084</v>
       </c>
       <c r="F35" s="12">
         <v>46063</v>
@@ -2428,10 +2425,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>55</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>7</v>
@@ -2458,10 +2455,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>56</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>57</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>7</v>
@@ -2479,7 +2476,7 @@
         <v>1510</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I37" s="11" t="str">
         <f t="shared" si="0"/>
@@ -2488,10 +2485,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>59</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -2509,7 +2506,7 @@
         <v>1510</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I38" s="11" t="str">
         <f t="shared" si="0"/>
@@ -2548,10 +2545,10 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>7</v>
@@ -2569,7 +2566,7 @@
         <v>1510</v>
       </c>
       <c r="H40" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I40" s="11" t="str">
         <f t="shared" ref="I40:I61" si="2">TEXT(D40,"mmmm")</f>
@@ -2578,10 +2575,10 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>85</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>86</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>7</v>
@@ -2599,7 +2596,7 @@
         <v>1510</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I41" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2638,10 +2635,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>90</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>7</v>
@@ -2659,7 +2656,7 @@
         <v>1510</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I43" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2668,10 +2665,10 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="17" t="s">
         <v>91</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>92</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>7</v>
@@ -2689,7 +2686,7 @@
         <v>1510</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I44" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2698,10 +2695,10 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="17" t="s">
         <v>93</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>94</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>7</v>
@@ -2719,7 +2716,7 @@
         <v>1510</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I45" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2728,10 +2725,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>7</v>
@@ -2749,7 +2746,7 @@
         <v>1510</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I46" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2758,10 +2755,10 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>108</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>7</v>
@@ -2779,7 +2776,7 @@
         <v>1510</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I47" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2788,10 +2785,10 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>7</v>
@@ -2809,7 +2806,7 @@
         <v>1510</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I48" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2818,10 +2815,10 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="17" t="s">
         <v>110</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>7</v>
@@ -2839,7 +2836,7 @@
         <v>1510</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I49" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2848,10 +2845,10 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" s="17" t="s">
         <v>117</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>118</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>7</v>
@@ -2869,7 +2866,7 @@
         <v>1510</v>
       </c>
       <c r="H50" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I50" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2878,10 +2875,10 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>7</v>
@@ -2899,7 +2896,7 @@
         <v>1510</v>
       </c>
       <c r="H51" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I51" s="11" t="str">
         <f t="shared" si="2"/>
@@ -3410,28 +3407,28 @@
         <v>0</v>
       </c>
       <c r="D3" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>81</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>82</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="26" t="s">
-        <v>84</v>
-      </c>
       <c r="K3" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -3472,7 +3469,7 @@
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
@@ -3486,64 +3483,64 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="F7" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="G7" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="H7" s="38" t="s">
         <v>5</v>
       </c>
       <c r="I7" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="38" t="s">
-        <v>84</v>
-      </c>
       <c r="K7" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="C8" t="str" cm="1">
-        <f t="array" ref="C8:K8">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!A2:A1000 = B8, "No hay datos para este conceptoo ")</f>
-        <v>T-4CI3L3</v>
+        <f t="array" ref="C8:K8">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!A2:A1000 = B8, "No hay datos para este concepto")</f>
+        <v>T-4CHWMB</v>
       </c>
       <c r="D8" t="str">
-        <v>CARMEN CECILIA FLORES GUTIERREZ</v>
+        <v>IUAN MARIA OSORNO VILLATORO</v>
       </c>
       <c r="E8" t="str">
         <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
       </c>
       <c r="F8" s="7">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="G8" s="7">
-        <v>46087</v>
+        <v>46084</v>
       </c>
       <c r="H8" s="7">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="I8" s="9">
-        <v>1510</v>
+        <v>8000</v>
       </c>
       <c r="J8" t="str">
-        <v>Aprovados</v>
+        <v>Entregado</v>
       </c>
       <c r="K8" t="str">
         <v>febrero</v>
@@ -3557,7 +3554,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="40"/>
       <c r="D12" s="40"/>
@@ -3571,34 +3568,34 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>0</v>
       </c>
       <c r="D13" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="F13" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="38" t="s">
+      <c r="G13" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="H13" s="38" t="s">
         <v>5</v>
       </c>
       <c r="I13" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="38" t="s">
-        <v>84</v>
-      </c>
       <c r="K13" s="32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
@@ -3645,7 +3642,7 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C18" s="40"/>
       <c r="D18" s="40"/>
@@ -3659,159 +3656,101 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>0</v>
       </c>
       <c r="D19" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="F19" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="38" t="s">
+      <c r="G19" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="G19" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="H19" s="38" t="s">
         <v>5</v>
       </c>
       <c r="I19" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>113</v>
+      <c r="K19" s="26" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="7">
-        <v>46070</v>
+        <v>46084</v>
       </c>
       <c r="C20" t="str" cm="1">
-        <f t="array" ref="C20:K23">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!E2:E1000= B20, "No hay datos para esta fecha")</f>
-        <v>T-4CHCQJ</v>
+        <f t="array" ref="C20:K20">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!E2:E1000= B20, "No hay datos para esta fecha")</f>
+        <v>T-4CHWMB</v>
       </c>
       <c r="D20" t="str">
-        <v xml:space="preserve">MILTON JAVIER ZAVALA </v>
+        <v>IUAN MARIA OSORNO VILLATORO</v>
       </c>
       <c r="E20" t="str">
         <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
       </c>
       <c r="F20" s="7">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="G20" s="7">
-        <v>46070</v>
+        <v>46084</v>
       </c>
       <c r="H20" s="7">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="I20" s="9">
-        <v>1510</v>
+        <v>8000</v>
       </c>
       <c r="J20" t="str">
         <v>Entregado</v>
       </c>
       <c r="K20" t="str">
-        <v>enero</v>
+        <v>febrero</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C21" t="str">
-        <v>T-4CHCPI</v>
-      </c>
-      <c r="D21" t="str">
-        <v xml:space="preserve">MILTON JAVIER ZAVALA </v>
-      </c>
-      <c r="E21" t="str">
-        <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
-      </c>
-      <c r="F21" s="7">
-        <v>46049</v>
-      </c>
-      <c r="G21" s="7">
-        <v>46070</v>
-      </c>
-      <c r="H21" s="7">
-        <v>46049</v>
-      </c>
-      <c r="I21" s="9">
-        <v>1510</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Entregado</v>
-      </c>
-      <c r="K21" t="str">
-        <v>enero</v>
-      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="9"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C22" t="str">
-        <v>T-4CHCQK</v>
-      </c>
-      <c r="D22" t="str">
-        <v xml:space="preserve">DIONICIO CUADRA KAUTZ </v>
-      </c>
-      <c r="E22" t="str">
-        <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
-      </c>
-      <c r="F22" s="7">
-        <v>46049</v>
-      </c>
-      <c r="G22" s="7">
-        <v>46070</v>
-      </c>
-      <c r="H22" s="7">
-        <v>46049</v>
-      </c>
-      <c r="I22" s="9">
-        <v>1510</v>
-      </c>
-      <c r="J22" t="str">
-        <v>Aprovados</v>
-      </c>
-      <c r="K22" t="str">
-        <v>enero</v>
-      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="9"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C23" t="str">
-        <v>T-4CHCQ0</v>
-      </c>
-      <c r="D23" t="str">
-        <v xml:space="preserve">DIONICIO CUADRA KAUTZ </v>
-      </c>
-      <c r="E23" t="str">
-        <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
-      </c>
-      <c r="F23" s="7">
-        <v>46049</v>
-      </c>
-      <c r="G23" s="7">
-        <v>46070</v>
-      </c>
-      <c r="H23" s="7">
-        <v>46049</v>
-      </c>
-      <c r="I23" s="9">
-        <v>1510</v>
-      </c>
-      <c r="J23" t="str">
-        <v>Aprovados</v>
-      </c>
-      <c r="K23" t="str">
-        <v>enero</v>
-      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -3825,34 +3764,34 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>0</v>
       </c>
       <c r="D27" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="38" t="s">
+      <c r="F27" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="38" t="s">
+      <c r="G27" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="H27" s="38" t="s">
         <v>5</v>
       </c>
       <c r="I27" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J27" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="38" t="s">
-        <v>84</v>
-      </c>
       <c r="K27" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
@@ -3983,7 +3922,7 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C34" s="40"/>
       <c r="D34" s="40"/>
@@ -4003,33 +3942,33 @@
         <v>0</v>
       </c>
       <c r="D35" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="38" t="s">
+      <c r="F35" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F35" s="38" t="s">
+      <c r="G35" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="H35" s="38" t="s">
         <v>5</v>
       </c>
       <c r="I35" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="J35" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J35" s="38" t="s">
-        <v>84</v>
-      </c>
       <c r="K35" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C36" t="str" cm="1">
         <f t="array" ref="C36:K41">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!H2:H1000= B36, "No hay registros")</f>

--- a/AÑO 2026/Registro bauchers.xlsx
+++ b/AÑO 2026/Registro bauchers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\AÑO 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7E5B4A-2F1C-470E-8056-7D50D48CB54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7E7EA1-8CCE-4172-8C0B-A022601F943A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
@@ -3433,35 +3433,36 @@
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C4" t="str" cm="1">
-        <f t="array" ref="C4:K4">_xlfn._xlws.FILTER(TablaDatos[],TablaDatos[Nombre del cliente]="BOSCO ROBERTO ZAMPIERI MORALES ","No hay registro")</f>
-        <v>T-4CHZ1Y</v>
+        <f t="array" ref="C4:K4">_xlfn._xlws.FILTER(TablaDatos[],TablaDatos[Nombre del cliente]="ROSA ESMERALDA CASTILLO CASTRO","No hay registro")</f>
+        <v>T-4CLI9I</v>
       </c>
       <c r="D4" t="str">
-        <v xml:space="preserve">BOSCO ROBERTO ZAMPIERI MORALES </v>
+        <v>ROSA ESMERALDA CASTILLO CASTRO</v>
       </c>
       <c r="E4" t="str">
         <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
       </c>
       <c r="F4" s="7">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="G4" s="7">
-        <v>46085</v>
+        <v>46099</v>
       </c>
       <c r="H4" s="7">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="I4" s="9">
         <v>1510</v>
       </c>
       <c r="J4" t="str">
-        <v>Entregado</v>
+        <v>Espera</v>
       </c>
       <c r="K4" t="str">
         <v>febrero</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D5" s="10"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>

--- a/AÑO 2026/Registro bauchers.xlsx
+++ b/AÑO 2026/Registro bauchers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\AÑO 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B7E7EA1-8CCE-4172-8C0B-A022601F943A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D5FCC-07E0-416D-B332-6BC759D9092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
   <sheets>
     <sheet name="BAUCHER 2026" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="140">
   <si>
     <t xml:space="preserve">Concepto </t>
   </si>
@@ -419,6 +419,69 @@
   </si>
   <si>
     <t>T-4CILBE</t>
+  </si>
+  <si>
+    <t>T-4CIVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YOJAIRA VANESKA ACEVEDO DELGADO </t>
+  </si>
+  <si>
+    <t>T-4CIVFN</t>
+  </si>
+  <si>
+    <t>MARIA LIDIA ACEVEDO DELGADO</t>
+  </si>
+  <si>
+    <t>T-4CIVH2</t>
+  </si>
+  <si>
+    <t>MARIA LOURDES MENA</t>
+  </si>
+  <si>
+    <t>T-4CIVMO</t>
+  </si>
+  <si>
+    <t>YADIRA ANTONIA ULLOA BERMUDEZ</t>
+  </si>
+  <si>
+    <t>T-4CIVOJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVA MARIA BERMUDEZ ULLOA </t>
+  </si>
+  <si>
+    <t>T-4CIVNN</t>
+  </si>
+  <si>
+    <t>MARTHA LILY ULLOA</t>
+  </si>
+  <si>
+    <t>T-4CIVJ6</t>
+  </si>
+  <si>
+    <t>OVILIA DEL SOCORRO ARGUELLO ROCHA</t>
+  </si>
+  <si>
+    <t>T-4CIVLY</t>
+  </si>
+  <si>
+    <t>T-4CIVI3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA ESTER HERNANDEZ </t>
+  </si>
+  <si>
+    <t>T-4CIVNL</t>
+  </si>
+  <si>
+    <t>ENA DEL SOCORRO ULLOA</t>
+  </si>
+  <si>
+    <t>T-4CIVKK</t>
+  </si>
+  <si>
+    <t>MARBELLI CONCEPCION ULLOA</t>
   </si>
 </sst>
 </file>
@@ -428,7 +491,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,8 +521,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -520,8 +590,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -680,11 +762,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -749,6 +844,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2904,157 +3006,333 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="21"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="1"/>
+      <c r="A52" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E52" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F52" s="15">
+        <v>46085</v>
+      </c>
+      <c r="G52" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I52" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="1"/>
+      <c r="A53" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E53" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F53" s="15">
+        <v>46085</v>
+      </c>
+      <c r="G53" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I53" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="21"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="1"/>
+      <c r="A54" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E54" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F54" s="15">
+        <v>46085</v>
+      </c>
+      <c r="G54" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I54" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="21"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="1"/>
+      <c r="A55" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E55" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F55" s="15">
+        <v>46085</v>
+      </c>
+      <c r="G55" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I55" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="21"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="1"/>
+      <c r="A56" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E56" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F56" s="15">
+        <v>46085</v>
+      </c>
+      <c r="G56" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I56" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="21"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="1"/>
+      <c r="A57" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E57" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F57" s="15">
+        <v>46085</v>
+      </c>
+      <c r="G57" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I57" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="21"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="1"/>
+      <c r="A58" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E58" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F58" s="44">
+        <v>46085</v>
+      </c>
+      <c r="G58" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I58" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="1"/>
+      <c r="A59" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E59" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F59" s="45">
+        <v>46085</v>
+      </c>
+      <c r="G59" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H59" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I59" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="21"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="1"/>
+      <c r="A60" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E60" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F60" s="44">
+        <v>46085</v>
+      </c>
+      <c r="G60" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I60" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="21"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="1"/>
+      <c r="A61" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E61" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F61" s="45">
+        <v>46085</v>
+      </c>
+      <c r="G61" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I61" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="34"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="1"/>
+      <c r="A62" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="14">
+        <v>46085</v>
+      </c>
+      <c r="E62" s="14">
+        <v>46106</v>
+      </c>
+      <c r="F62" s="44">
+        <v>46085</v>
+      </c>
+      <c r="G62" s="13">
+        <v>1510</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I62" s="11" t="str">
         <f t="shared" ref="I62:I69" si="3">TEXT(D62,"mmmm")</f>
-        <v>enero</v>
+        <v>marzo</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -3065,7 +3343,7 @@
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
       <c r="G63" s="13"/>
-      <c r="H63" s="1"/>
+      <c r="H63" s="22"/>
       <c r="I63" s="11" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3079,7 +3357,7 @@
       <c r="E64" s="11"/>
       <c r="F64" s="11"/>
       <c r="G64" s="13"/>
-      <c r="H64" s="1"/>
+      <c r="H64" s="22"/>
       <c r="I64" s="11" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3093,7 +3371,7 @@
       <c r="E65" s="11"/>
       <c r="F65" s="11"/>
       <c r="G65" s="13"/>
-      <c r="H65" s="1"/>
+      <c r="H65" s="22"/>
       <c r="I65" s="11" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3107,7 +3385,7 @@
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
       <c r="G66" s="13"/>
-      <c r="H66" s="1"/>
+      <c r="H66" s="22"/>
       <c r="I66" s="11" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3121,7 +3399,7 @@
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
       <c r="G67" s="13"/>
-      <c r="H67" s="1"/>
+      <c r="H67" s="22"/>
       <c r="I67" s="11" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3135,7 +3413,7 @@
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
       <c r="G68" s="13"/>
-      <c r="H68" s="1"/>
+      <c r="H68" s="22"/>
       <c r="I68" s="11" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3149,7 +3427,7 @@
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
       <c r="G69" s="37"/>
-      <c r="H69" s="4"/>
+      <c r="H69" s="43"/>
       <c r="I69" s="14" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3163,7 +3441,7 @@
       <c r="E70" s="11"/>
       <c r="F70" s="11"/>
       <c r="G70" s="13"/>
-      <c r="H70" s="1"/>
+      <c r="H70" s="22"/>
       <c r="I70" s="11" t="str">
         <f t="shared" ref="I70:I83" si="4">TEXT(D70,"mmmm")</f>
         <v>enero</v>

--- a/AÑO 2026/Registro bauchers.xlsx
+++ b/AÑO 2026/Registro bauchers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\AÑO 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E53D5FCC-07E0-416D-B332-6BC759D9092B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB04EF2-5935-4A1D-A505-F4BCF87649BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -491,7 +491,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,6 +524,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -779,7 +786,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -836,6 +843,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -845,13 +859,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2435,7 +2443,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>21</v>
       </c>
@@ -2465,7 +2473,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>22</v>
       </c>
@@ -2495,7 +2503,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
         <v>23</v>
       </c>
@@ -2525,7 +2533,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>53</v>
       </c>
@@ -2555,7 +2563,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>55</v>
       </c>
@@ -2584,8 +2592,9 @@
         <f t="shared" si="0"/>
         <v>febrero</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="46"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>57</v>
       </c>
@@ -2615,7 +2624,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
         <v>6</v>
       </c>
@@ -2645,7 +2654,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>75</v>
       </c>
@@ -2675,7 +2684,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>84</v>
       </c>
@@ -2705,7 +2714,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>6</v>
       </c>
@@ -2735,7 +2744,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>88</v>
       </c>
@@ -2765,7 +2774,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>90</v>
       </c>
@@ -2795,7 +2804,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>92</v>
       </c>
@@ -2825,7 +2834,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>104</v>
       </c>
@@ -2855,7 +2864,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>106</v>
       </c>
@@ -2885,7 +2894,7 @@
         <v>febrero</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>108</v>
       </c>
@@ -3201,7 +3210,7 @@
       <c r="E58" s="14">
         <v>46106</v>
       </c>
-      <c r="F58" s="44">
+      <c r="F58" s="41">
         <v>46085</v>
       </c>
       <c r="G58" s="13">
@@ -3231,7 +3240,7 @@
       <c r="E59" s="14">
         <v>46106</v>
       </c>
-      <c r="F59" s="45">
+      <c r="F59" s="42">
         <v>46085</v>
       </c>
       <c r="G59" s="13">
@@ -3261,7 +3270,7 @@
       <c r="E60" s="14">
         <v>46106</v>
       </c>
-      <c r="F60" s="44">
+      <c r="F60" s="41">
         <v>46085</v>
       </c>
       <c r="G60" s="13">
@@ -3291,7 +3300,7 @@
       <c r="E61" s="14">
         <v>46106</v>
       </c>
-      <c r="F61" s="45">
+      <c r="F61" s="42">
         <v>46085</v>
       </c>
       <c r="G61" s="13">
@@ -3321,7 +3330,7 @@
       <c r="E62" s="14">
         <v>46106</v>
       </c>
-      <c r="F62" s="44">
+      <c r="F62" s="41">
         <v>46085</v>
       </c>
       <c r="G62" s="13">
@@ -3427,7 +3436,7 @@
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
       <c r="G69" s="37"/>
-      <c r="H69" s="43"/>
+      <c r="H69" s="40"/>
       <c r="I69" s="14" t="str">
         <f t="shared" si="3"/>
         <v>enero</v>
@@ -3668,17 +3677,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C3" s="26" t="s">
@@ -3711,23 +3720,23 @@
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C4" t="str" cm="1">
-        <f t="array" ref="C4:K4">_xlfn._xlws.FILTER(TablaDatos[],TablaDatos[Nombre del cliente]="ROSA ESMERALDA CASTILLO CASTRO","No hay registro")</f>
-        <v>T-4CLI9I</v>
+        <f t="array" ref="C4:K4">_xlfn._xlws.FILTER(TablaDatos[],TablaDatos[Nombre del cliente]="JAVIER HERNANDEZ RUIZ","No hay registro")</f>
+        <v>T-4CI5SV</v>
       </c>
       <c r="D4" t="str">
-        <v>ROSA ESMERALDA CASTILLO CASTRO</v>
+        <v>JAVIER HERNANDEZ RUIZ</v>
       </c>
       <c r="E4" t="str">
         <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
       </c>
       <c r="F4" s="7">
-        <v>46078</v>
+        <v>46069</v>
       </c>
       <c r="G4" s="7">
-        <v>46099</v>
+        <v>46090</v>
       </c>
       <c r="H4" s="7">
-        <v>46078</v>
+        <v>46069</v>
       </c>
       <c r="I4" s="9">
         <v>1510</v>
@@ -3747,18 +3756,18 @@
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
@@ -3832,18 +3841,18 @@
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
@@ -3920,18 +3929,18 @@
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="38" t="s">
@@ -4028,18 +4037,18 @@
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="38" t="s">
@@ -4200,18 +4209,18 @@
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="26" t="s">
